--- a/information_request_forms/009_store_locator_search_form--information_request_forms.xlsx
+++ b/information_request_forms/009_store_locator_search_form--information_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -888,8 +888,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -917,12 +917,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'retail_stores'}</t>
+          <t>retail_stores</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Retail Stores'}</t>
+          <t>Retail Stores</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'service_centers'}</t>
+          <t>service_centers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Service Centers'}</t>
+          <t>Service Centers</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'pharmacies'}</t>
+          <t>pharmacies</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Pharmacies'}</t>
+          <t>Pharmacies</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'banks'}</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Banks'}</t>
+          <t>Banks</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'restaurants'}</t>
+          <t>restaurants</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Restaurants'}</t>
+          <t>Restaurants</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'downtown'}</t>
+          <t>downtown</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Downtown'}</t>
+          <t>Downtown</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'uptown'}</t>
+          <t>uptown</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Uptown'}</t>
+          <t>Uptown</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'mall'}</t>
+          <t>mall</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Mall'}</t>
+          <t>Mall</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'alphabetically'}</t>
+          <t>alphabetically</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Alphabetically'}</t>
+          <t>Alphabetically</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'distance'}</t>
+          <t>distance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Distance'}</t>
+          <t>Distance</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'1-5_miles'}</t>
+          <t>1-5_miles</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': '1-5 Miles'}</t>
+          <t>1-5 Miles</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'6-10_miles'}</t>
+          <t>6-10_miles</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': '6-10 Miles'}</t>
+          <t>6-10 Miles</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_10_miles'}</t>
+          <t>more_than_10_miles</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'More Than 10 Miles'}</t>
+          <t>More Than 10 Miles</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'kilometers'}</t>
+          <t>kilometers</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Kilometers'}</t>
+          <t>Kilometers</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'miles'}</t>
+          <t>miles</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Miles'}</t>
+          <t>Miles</t>
         </is>
       </c>
     </row>
